--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5877" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5876" uniqueCount="780">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -267,7 +267,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() or value.exists() or dataAbsentReason.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() or value.exists() or dataAbsentReason.exists()}allgemeine-kultur-method-with-neutral-code:If the method-neutral code 41852-5 is used, Observation.method SHALL be present, because only the method identifies the investigation as a culture. {code.coding.where(system = 'http://loinc.org' and code = '41852-5').exists() implies method.exists()}</t>
   </si>
   <si>
     <t>Observation.id</t>
@@ -1349,6 +1349,9 @@
 </t>
   </si>
   <si>
+    <t>Bevorzugt 11475-1 'Microorganism identified in Specimen by Culture'. 41852-5 'Microorganism or agent identified in Specimen' ist gleichwertig zulaessig, weil das EU-Datenmodell die Methode nach Observation.method auslagert; derselbe Code steht auch bei der Allgemeinen Bestimmung, dort mit einem Organismus als Ergebnis. Bei 41852-5 ist Observation.method deshalb Pflicht (allgemeine-kultur-method-with-neutral-code). Siehe die Seite 'Profilauswahl und Abgrenzung'.</t>
+  </si>
+  <si>
     <t>LOINC-Code, der den gemessenen Laborparameter bzw. durchgeführten Labortest beschreibt.</t>
   </si>
   <si>
@@ -1358,18 +1361,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="11475-1"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-allgemeine-kultur-tests-loinc</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -2129,7 +2121,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
 </t>
   </si>
   <si>
@@ -2409,6 +2401,12 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -9708,16 +9706,16 @@
         <v>283</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>64</v>
+        <v>423</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9727,7 +9725,7 @@
         <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>426</v>
+        <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>77</v>
@@ -9742,13 +9740,11 @@
         <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y68" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y68" s="2"/>
+      <c r="Z68" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>77</v>
@@ -9783,10 +9779,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9883,10 +9879,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9985,10 +9981,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10087,10 +10083,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10187,10 +10183,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10289,10 +10285,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10393,10 +10389,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10495,10 +10491,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10599,10 +10595,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10703,10 +10699,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10807,13 +10803,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>77</v>
@@ -10857,7 +10853,7 @@
         <v>77</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>77</v>
@@ -10875,10 +10871,10 @@
         <v>142</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Z79" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>77</v>
@@ -10913,10 +10909,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11017,10 +11013,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11043,19 +11039,19 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11104,7 +11100,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
@@ -11121,10 +11117,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11221,10 +11217,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11323,10 +11319,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11352,13 +11348,13 @@
         <v>99</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11408,16 +11404,16 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI84" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>92</v>
@@ -11425,10 +11421,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11454,13 +11450,13 @@
         <v>126</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11489,28 +11485,28 @@
         <v>142</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z85" t="s" s="2">
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -11527,10 +11523,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11556,13 +11552,13 @@
         <v>259</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11612,7 +11608,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
@@ -11629,10 +11625,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11658,13 +11654,13 @@
         <v>99</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11714,7 +11710,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -11731,10 +11727,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11757,16 +11753,16 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11816,7 +11812,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
@@ -11833,14 +11829,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11859,19 +11855,19 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -11920,7 +11916,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -11937,10 +11933,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12037,10 +12033,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12139,10 +12135,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12168,13 +12164,13 @@
         <v>99</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12224,16 +12220,16 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI92" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>92</v>
@@ -12241,10 +12237,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12270,13 +12266,13 @@
         <v>126</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12305,28 +12301,28 @@
         <v>142</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z93" t="s" s="2">
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
@@ -12343,10 +12339,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12372,13 +12368,13 @@
         <v>259</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12428,7 +12424,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -12445,10 +12441,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12474,13 +12470,13 @@
         <v>99</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12530,7 +12526,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
@@ -12547,14 +12543,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12573,19 +12569,19 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
@@ -12634,7 +12630,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
@@ -12646,15 +12642,15 @@
         <v>91</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12751,10 +12747,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12853,13 +12849,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>104</v>
@@ -12881,13 +12877,13 @@
         <v>77</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>108</v>
@@ -12957,10 +12953,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12983,13 +12979,13 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13040,7 +13036,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -13057,10 +13053,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13086,13 +13082,13 @@
         <v>120</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13142,7 +13138,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -13159,10 +13155,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13185,19 +13181,19 @@
         <v>85</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>389</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -13246,7 +13242,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -13263,10 +13259,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13292,16 +13288,16 @@
         <v>283</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13338,26 +13334,26 @@
         <v>77</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE103" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI103" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>92</v>
@@ -13365,13 +13361,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>77</v>
@@ -13396,16 +13392,16 @@
         <v>283</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="N104" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -13434,7 +13430,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>77</v>
@@ -13452,7 +13448,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -13461,7 +13457,7 @@
         <v>84</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>92</v>
@@ -13469,10 +13465,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13569,10 +13565,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13671,10 +13667,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13775,10 +13771,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13875,10 +13871,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13977,10 +13973,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14081,10 +14077,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14183,10 +14179,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14287,10 +14283,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14391,10 +14387,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14495,10 +14491,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14599,13 +14595,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C116" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>77</v>
@@ -14627,19 +14623,19 @@
         <v>85</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M116" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="N116" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O116" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -14688,7 +14684,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>
@@ -14697,7 +14693,7 @@
         <v>84</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>92</v>
@@ -14705,10 +14701,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14805,10 +14801,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14907,13 +14903,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C119" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>104</v>
@@ -14935,16 +14931,16 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15011,10 +15007,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B120" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15037,19 +15033,19 @@
         <v>85</v>
       </c>
       <c r="K120" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L120" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L120" t="s" s="2">
+      <c r="M120" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -15098,7 +15094,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>75</v>
@@ -15115,10 +15111,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B121" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15215,10 +15211,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15317,13 +15313,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>104</v>
@@ -15345,16 +15341,16 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -15421,10 +15417,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15447,13 +15443,13 @@
         <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -15504,7 +15500,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>75</v>
@@ -15521,10 +15517,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15550,22 +15546,22 @@
         <v>160</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>328</v>
       </c>
       <c r="O125" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q125" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q125" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="R125" t="s" s="2">
         <v>77</v>
@@ -15589,28 +15585,28 @@
         <v>226</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="Z125" t="s" s="2">
+      <c r="AA125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF125" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
@@ -15627,10 +15623,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15656,16 +15652,16 @@
         <v>99</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>328</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -15714,7 +15710,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
@@ -15731,10 +15727,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15760,74 +15756,74 @@
         <v>126</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF127" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="S127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF127" t="s" s="2">
+      <c r="AG127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI127" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>92</v>
@@ -15835,10 +15831,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15864,16 +15860,16 @@
         <v>160</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>77</v>
@@ -15922,7 +15918,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>75</v>
@@ -15939,13 +15935,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C129" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>77</v>
@@ -15967,19 +15963,19 @@
         <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M129" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="N129" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O129" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>77</v>
@@ -16028,7 +16024,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
@@ -16037,7 +16033,7 @@
         <v>84</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>92</v>
@@ -16045,13 +16041,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C130" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>77</v>
@@ -16073,19 +16069,19 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M130" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="N130" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O130" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>77</v>
@@ -16134,7 +16130,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>75</v>
@@ -16143,7 +16139,7 @@
         <v>84</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>92</v>
@@ -16151,10 +16147,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16180,16 +16176,16 @@
         <v>283</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -16218,34 +16214,34 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI131" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>92</v>
@@ -16253,14 +16249,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -16282,16 +16278,16 @@
         <v>283</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -16319,11 +16315,11 @@
         <v>142</v>
       </c>
       <c r="Y132" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="Z132" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="Z132" t="s" s="2">
-        <v>640</v>
-      </c>
       <c r="AA132" t="s" s="2">
         <v>77</v>
       </c>
@@ -16340,7 +16336,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -16357,10 +16353,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16383,19 +16379,19 @@
         <v>77</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
@@ -16444,7 +16440,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
@@ -16461,10 +16457,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16490,13 +16486,13 @@
         <v>283</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -16525,11 +16521,11 @@
         <v>150</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="Z134" t="s" s="2">
-        <v>652</v>
-      </c>
       <c r="AA134" t="s" s="2">
         <v>77</v>
       </c>
@@ -16546,7 +16542,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>75</v>
@@ -16563,10 +16559,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16592,16 +16588,16 @@
         <v>283</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -16630,7 +16626,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -16648,7 +16644,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>75</v>
@@ -16665,10 +16661,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16765,10 +16761,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16867,10 +16863,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16971,10 +16967,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17071,10 +17067,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17173,10 +17169,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17277,10 +17273,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17379,10 +17375,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17483,10 +17479,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17587,10 +17583,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17691,10 +17687,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17795,10 +17791,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17821,16 +17817,16 @@
         <v>77</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -17880,7 +17876,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>75</v>
@@ -17897,10 +17893,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17997,10 +17993,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18099,10 +18095,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18128,13 +18124,13 @@
         <v>99</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -18184,16 +18180,16 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI150" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>92</v>
@@ -18201,10 +18197,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18230,13 +18226,13 @@
         <v>126</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -18265,28 +18261,28 @@
         <v>142</v>
       </c>
       <c r="Y151" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z151" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z151" t="s" s="2">
+      <c r="AA151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF151" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>75</v>
@@ -18303,10 +18299,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18332,13 +18328,13 @@
         <v>259</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -18388,7 +18384,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>75</v>
@@ -18405,10 +18401,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18434,13 +18430,13 @@
         <v>99</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -18490,7 +18486,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>75</v>
@@ -18507,10 +18503,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18533,16 +18529,16 @@
         <v>77</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -18592,7 +18588,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>75</v>
@@ -18609,10 +18605,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18709,10 +18705,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18811,10 +18807,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18840,13 +18836,13 @@
         <v>99</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -18896,16 +18892,16 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI157" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>92</v>
@@ -18913,10 +18909,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18942,13 +18938,13 @@
         <v>126</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -18977,28 +18973,28 @@
         <v>142</v>
       </c>
       <c r="Y158" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z158" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z158" t="s" s="2">
+      <c r="AA158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF158" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>75</v>
@@ -19015,10 +19011,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19044,13 +19040,13 @@
         <v>259</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -19100,7 +19096,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>75</v>
@@ -19117,10 +19113,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19146,13 +19142,13 @@
         <v>99</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -19202,7 +19198,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>75</v>
@@ -19219,10 +19215,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19245,19 +19241,19 @@
         <v>77</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="N161" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="N161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>77</v>
@@ -19306,7 +19302,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>75</v>
@@ -19318,15 +19314,15 @@
         <v>91</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19423,10 +19419,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19525,14 +19521,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -19554,10 +19550,10 @@
         <v>105</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>108</v>
@@ -19612,7 +19608,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>75</v>
@@ -19629,10 +19625,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19655,16 +19651,16 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L165" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="L165" t="s" s="2">
+      <c r="M165" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -19714,7 +19710,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>75</v>
@@ -19723,18 +19719,18 @@
         <v>84</v>
       </c>
       <c r="AI165" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="AJ165" t="s" s="2">
-        <v>712</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19757,16 +19753,16 @@
         <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="M166" t="s" s="2">
-        <v>715</v>
-      </c>
       <c r="N166" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -19816,7 +19812,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>75</v>
@@ -19825,18 +19821,18 @@
         <v>84</v>
       </c>
       <c r="AI166" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="AJ166" t="s" s="2">
-        <v>712</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19862,16 +19858,16 @@
         <v>283</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>77</v>
@@ -19899,11 +19895,11 @@
         <v>164</v>
       </c>
       <c r="Y167" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="Z167" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="Z167" t="s" s="2">
-        <v>722</v>
-      </c>
       <c r="AA167" t="s" s="2">
         <v>77</v>
       </c>
@@ -19920,7 +19916,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>75</v>
@@ -19937,10 +19933,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19966,16 +19962,16 @@
         <v>283</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -20003,11 +19999,11 @@
         <v>150</v>
       </c>
       <c r="Y168" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="Z168" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="Z168" t="s" s="2">
-        <v>729</v>
-      </c>
       <c r="AA168" t="s" s="2">
         <v>77</v>
       </c>
@@ -20024,7 +20020,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>75</v>
@@ -20041,10 +20037,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20067,19 +20063,19 @@
         <v>77</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -20128,7 +20124,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>75</v>
@@ -20140,15 +20136,15 @@
         <v>91</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20174,10 +20170,10 @@
         <v>99</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="N170" t="s" s="2">
         <v>328</v>
@@ -20230,7 +20226,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>75</v>
@@ -20247,10 +20243,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20273,16 +20269,16 @@
         <v>85</v>
       </c>
       <c r="K171" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="L171" t="s" s="2">
         <v>740</v>
       </c>
-      <c r="L171" t="s" s="2">
+      <c r="M171" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20332,7 +20328,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>75</v>
@@ -20349,10 +20345,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20375,16 +20371,16 @@
         <v>85</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>745</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -20434,7 +20430,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>75</v>
@@ -20451,10 +20447,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20477,19 +20473,19 @@
         <v>85</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>750</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>751</v>
       </c>
-      <c r="N173" t="s" s="2">
+      <c r="O173" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>77</v>
@@ -20538,7 +20534,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
@@ -20555,10 +20551,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20655,10 +20651,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20757,14 +20753,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -20786,10 +20782,10 @@
         <v>105</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>108</v>
@@ -20844,7 +20840,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>75</v>
@@ -20861,10 +20857,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20890,16 +20886,16 @@
         <v>283</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="N177" t="s" s="2">
-        <v>760</v>
-      </c>
       <c r="O177" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -20927,10 +20923,10 @@
         <v>150</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>427</v>
+        <v>760</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>428</v>
+        <v>761</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>77</v>
@@ -20948,7 +20944,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>84</v>
@@ -20965,10 +20961,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20991,19 +20987,19 @@
         <v>85</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>77</v>
@@ -21052,7 +21048,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>75</v>
@@ -21069,10 +21065,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21098,16 +21094,16 @@
         <v>283</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
@@ -21135,10 +21131,10 @@
         <v>142</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>77</v>
@@ -21156,7 +21152,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>75</v>
@@ -21165,7 +21161,7 @@
         <v>84</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>92</v>
@@ -21173,14 +21169,14 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
@@ -21202,16 +21198,16 @@
         <v>283</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N180" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="O180" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>77</v>
@@ -21239,10 +21235,10 @@
         <v>142</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>77</v>
@@ -21260,7 +21256,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>75</v>
@@ -21277,10 +21273,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21306,16 +21302,16 @@
         <v>78</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N181" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="O181" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>77</v>
@@ -21364,7 +21360,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>75</v>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-allgemeine-kultur.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
